--- a/datos.xlsx
+++ b/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\OneDrive\Documentos\GitHub\script-agroads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBA4FF53-04C9-4C23-8E94-4155F7A25BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E6E506-5BD3-4E7D-A124-DCD72C40AF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F5D4C408-2A4F-4C50-9972-0D53A81D9D1D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="155">
   <si>
     <t>Maquinaria agricola</t>
   </si>
@@ -65,7 +65,99 @@
     <t>anio</t>
   </si>
   <si>
+    <t>modelo</t>
+  </si>
+  <si>
+    <t>hp</t>
+  </si>
+  <si>
+    <t>horas</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>categoria</t>
+  </si>
+  <si>
+    <t>sub_tipo</t>
+  </si>
+  <si>
+    <t>sub_sub_tipo</t>
+  </si>
+  <si>
+    <t>titulo</t>
+  </si>
+  <si>
+    <t>moneda</t>
+  </si>
+  <si>
+    <t>monto</t>
+  </si>
+  <si>
+    <t>dto_pago</t>
+  </si>
+  <si>
+    <t>pesos</t>
+  </si>
+  <si>
+    <t>condicion</t>
+  </si>
+  <si>
+    <t>Tractor Fiat 880 - 5</t>
+  </si>
+  <si>
+    <t>dólar</t>
+  </si>
+  <si>
+    <t>Fiat</t>
+  </si>
+  <si>
+    <t>880-5</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>Tractores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agricolas </t>
+  </si>
+  <si>
+    <t>De tracción simple</t>
+  </si>
+  <si>
+    <t>Tractor Deutz A65 con Cabina Motor 2114 con Caja de Quinta</t>
+  </si>
+  <si>
+    <t>Deutz</t>
+  </si>
+  <si>
+    <t>AX 120</t>
+  </si>
+  <si>
+    <t>A65</t>
+  </si>
+  <si>
+    <t>No lo se</t>
+  </si>
+  <si>
     <t>CISTERNA TALLER VARIOS COMPARTIMIENTOS.
+USADO
+Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
 USADO
 Visita nuestro perfil para conocer nuestro stock.
 Contamos con más de 300 implementos disponibles
@@ -73,70 +165,521 @@
 TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
   </si>
   <si>
-    <t>modelo</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>horas</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>categoria</t>
-  </si>
-  <si>
-    <t>sub_tipo</t>
-  </si>
-  <si>
-    <t>sub_sub_tipo</t>
-  </si>
-  <si>
-    <t>titulo</t>
-  </si>
-  <si>
-    <t>moneda</t>
-  </si>
-  <si>
-    <t>monto</t>
-  </si>
-  <si>
-    <t>dto_pago</t>
-  </si>
-  <si>
-    <t>pesos</t>
-  </si>
-  <si>
-    <t>condicion</t>
-  </si>
-  <si>
-    <t>Tractor Fiat 880 - 5</t>
-  </si>
-  <si>
-    <t>dólar</t>
-  </si>
-  <si>
-    <t>Fiat</t>
-  </si>
-  <si>
-    <t>880-5</t>
-  </si>
-  <si>
-    <t>descripcion</t>
-  </si>
-  <si>
-    <t>Tractores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agricolas </t>
-  </si>
-  <si>
-    <t>De tracción simple</t>
+    <t>Articulados</t>
+  </si>
+  <si>
+    <t>Tractor Articulado Motor Deutz Pr160</t>
+  </si>
+  <si>
+    <t>Tractor Deutz A85 sin cabina</t>
+  </si>
+  <si>
+    <t>A85</t>
+  </si>
+  <si>
+    <t>Tractor Fiat 55 Hp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiat </t>
+  </si>
+  <si>
+    <t>Tractor Mf 1195 Massey Ferguson</t>
+  </si>
+  <si>
+    <t>Tractor Mf 1360 Massey Ferguson</t>
+  </si>
+  <si>
+    <t>Massey Ferguson</t>
+  </si>
+  <si>
+    <t>MF 1195 S 2</t>
+  </si>
+  <si>
+    <t>1360 S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tractor Valmet Turbo 1780 180 Hp </t>
+  </si>
+  <si>
+    <t>De tracción doble</t>
+  </si>
+  <si>
+    <t>Valmet</t>
+  </si>
+  <si>
+    <t>Tractor Zanello Up-10 Impecable</t>
+  </si>
+  <si>
+    <t>Zanello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UP 10 </t>
+  </si>
+  <si>
+    <t>Tractor Lovol 25 Hp - 4x4 - 3 Puntos - Salida Hidráulica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lovol </t>
+  </si>
+  <si>
+    <t>TE &gt; 254</t>
+  </si>
+  <si>
+    <t>Tractor Hanomag  3 Puntos Y Salida Hidraulica.</t>
+  </si>
+  <si>
+    <t>Hanomag</t>
+  </si>
+  <si>
+    <t>Otro modelo</t>
+  </si>
+  <si>
+    <t>Tractor HANOMAG 25 HP  3 puntos y salida hidraulica.
+ , MOTOR HECHO NUEVO.Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolvas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodescargables </t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 14 toneladas favorito</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 8 toneladas Leval</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 14 toneladas Impar Reparada.</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 14 toneladas Agromec</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 14 toneladas Cestari</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 8 toneladas Montecor</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 8 tn Ambroggio con balanza</t>
+  </si>
+  <si>
+    <t>Ambroggio</t>
+  </si>
+  <si>
+    <t>Akron</t>
+  </si>
+  <si>
+    <t>Leval</t>
+  </si>
+  <si>
+    <t>Agromec</t>
+  </si>
+  <si>
+    <t>Cestari</t>
+  </si>
+  <si>
+    <t>Montecor</t>
+  </si>
+  <si>
+    <t>Mancini</t>
+  </si>
+  <si>
+    <t>De Grande</t>
+  </si>
+  <si>
+    <t>El Sol</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 18 tn De Grande c balanza</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 30 tn El Sol con balanza</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 14 tn Mancini Reparada</t>
+  </si>
+  <si>
+    <t>Tolva autodescargable monotolva 14 tn Akron con balanza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisterna </t>
+  </si>
+  <si>
+    <t>Acoplado Cisterna 2000 Lts</t>
+  </si>
+  <si>
+    <t>Acoplado Cisterna Mauro 3000 Lts</t>
+  </si>
+  <si>
+    <t>Acoplado Cisterna Mauro 3000 Litros  En Tucumán</t>
+  </si>
+  <si>
+    <t>Carreton Hidraulico 8 Toneladas Acepla 8tn Rojo</t>
+  </si>
+  <si>
+    <t>Cisterna Agromec 3000 Litros En Cordoba</t>
+  </si>
+  <si>
+    <t>Cisterna Gentili 3000 Lts Precio Nueva</t>
+  </si>
+  <si>
+    <t>Mauro</t>
+  </si>
+  <si>
+    <t>MAS CISTERNAS DISPONIBLES NUEVAS Y USADAS CONTACTANOS.                                Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Acoplado Playo Con Barandas 6 toneladas</t>
+  </si>
+  <si>
+    <t>Acoplado playo Rural Agromec 4 Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carretones </t>
+  </si>
+  <si>
+    <t>Nuevo</t>
+  </si>
+  <si>
+    <t>Jacto</t>
+  </si>
+  <si>
+    <t>Fraga</t>
+  </si>
+  <si>
+    <t>MAS ACOPLADOS DISPONIBLES NUEVAS Y USADAS CONTACTANOS.                                Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Especificaciones técnicas:
+✔️ Carga máxima: 4000 kg
+✔️ Largo: 5000 mm
+✔️ Ancho: 1940 mm
+✔️ Peso: 765 kg
+✔️ Trocha: 1520 mm
+✔️ Rodado: 750 x 18”
+Construcción:
+✔️ Chasis reforzado de alta durabilidad
+✔️ Piso de chapa antideslizante
+✔️ 4 barandas rebatibles y desmontables
+✔️ Estructura sólida y apta para trabajo intensivo
+Equipamiento:
+✔️ Sistema de enganche seguro
+✔️ Ideal para uso rural, transporte de insumos y materiales
+✔️ Excelente estabilidad y maniobrabilidad                                                                   MAS ACOPLADOS DISPONIBLES NUEVAS Y USADAS CONTACTANOS.                                Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Acoplado Tanque 2000 Litros  Jacto Yomel</t>
+  </si>
+  <si>
+    <t>Tanque</t>
+  </si>
+  <si>
+    <t>Taller</t>
+  </si>
+  <si>
+    <t>Gentili</t>
+  </si>
+  <si>
+    <t>MAS TANQUES DISPONIBLES NUEVAS Y USADAS CONTACTANOS.                                Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Volcadores</t>
+  </si>
+  <si>
+    <t>El Grillo</t>
+  </si>
+  <si>
+    <t>Acoplado Volcador El Grillo De 4 Toneladas Tn 3 Vuelcos</t>
+  </si>
+  <si>
+    <t>ATF - 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acoplado carreton Trailer Agricola Mancini 3 Ejes Camion </t>
+  </si>
+  <si>
+    <t>Trailer</t>
+  </si>
+  <si>
+    <t>Acepla</t>
+  </si>
+  <si>
+    <t>playo</t>
+  </si>
+  <si>
+    <t>Forrajeros</t>
+  </si>
+  <si>
+    <t>Acoplado Carro Forrajero Fraga Usado</t>
+  </si>
+  <si>
+    <t>Carro Taller de 5 Metros</t>
+  </si>
+  <si>
+    <t>Agrofenix</t>
+  </si>
+  <si>
+    <t>Acoplado Cisterna 3000l Con Bomba</t>
+  </si>
+  <si>
+    <t>CISTERNA GENTILI 
+CAPACIDAD PARA 3000 LTS
+2 EJES
+CHASIS ROBUSTO  MAS cisternas DISPONIBLES NUEVAS Y USADAS CONTACTANOS.                                Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>CISTERNA AGROMEC
+CAPACIDAD PARA 3000 LTS
+2 EJES
+CHASIS ROBUSTO  MAS cisternas DISPONIBLES NUEVAS Y USADAS CONTACTANOS.                                Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Cisterna Y Taller DE 3000 Litros</t>
+  </si>
+  <si>
+    <t>MAS DESMALEZADORAS DISPONIBLES DE TODAS LAS MEDIDAS, USADAS Y NUEVA COMUNICATE.                           Contamos con más de 300 implementos disponibles
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Desmalezadoras</t>
+  </si>
+  <si>
+    <t>De arrastre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desmalezadora Bernardin 3000 3 metros </t>
+  </si>
+  <si>
+    <t>Desmalezadora Cerutti 3 Metros plegable</t>
+  </si>
+  <si>
+    <t>Cerutti</t>
+  </si>
+  <si>
+    <t>BERNARDIN</t>
+  </si>
+  <si>
+    <t>Desmalezadora Hileradora 3 Metros Agromec</t>
+  </si>
+  <si>
+    <t>Bellmaq</t>
+  </si>
+  <si>
+    <t>Yomel</t>
+  </si>
+  <si>
+    <t>Desmalezadora 3 puntos Yomel 1520 1,5 metros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desmalezadora 3 Puntos Bellmaq De 1,5 metros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desmalezadora Bernardin 1500 De 1,5 metros </t>
+  </si>
+  <si>
+    <t>Desmalezadora de arrastre Agromec de 1,5 metros</t>
+  </si>
+  <si>
+    <t>Desmalezadora de arrastre Ja - Ma De 1,5 Mts</t>
+  </si>
+  <si>
+    <t>Desmalezadora De 1,80 Metros 3 Puntos King Kutter Usa</t>
+  </si>
+  <si>
+    <t>De montado</t>
+  </si>
+  <si>
+    <t>Desmalezadora De Arrastre De 1,5 Mts</t>
+  </si>
+  <si>
+    <t>CASILLAS RURALES - "La Criolla" - Linea 2026
+Cuentan con TERMOTANQUE, TOLDO, BAULERA, INSTALACIÓN DE AGUA y ELÉCTRICA.
+AISLANTE: TERGOPOL.
+Disponibles en distintas medidas:
+✔️ 4,5 m – 2 camas - 14800 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 5,5 m – 4 camas - 16300 + IVA - DISPONIBLE ENTREGA INMEDIATA
+✔️ 6,5 m – 4 camas - 19900 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 7,5 m – 6 camas - 21400 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 8,5 m – 6 camas - 24000 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ Modelos personalizados a pedido
+Para mas informacion sobre financiacion, precios y fotos de cada casilla en especifico no dudes en consultarnos.
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+CASILLAS RURALES - "La Criolla" - Linea 2026
+Cuentan con TERMOTANQUE, TOLDO, BAULERA, INSTALACIÓN DE AGUA y ELÉCTRICA.
+AISLANTE: TERGOPOL.
+Disponibles en distintas medidas:
+✔️ 4,5 m – 2 camas - 14800 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 5,5 m – 4 camas - 16300 + IVA - DISPONIBLE ENTREGA INMEDIATA
+✔️ 6,5 m – 4 camas - 19900 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 7,5 m – 6 camas - 21400 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 8,5 m – 6 camas - 24000 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ Modelos personalizados a pedido
+Para mas informacion sobre financiacion, precios y fotos de cada casilla en especifico no dudes en consultarnos.
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>Casillas Rurales</t>
+  </si>
+  <si>
+    <t>Casillas Rurales la Criolla 2026 - 4,5/5.5/6.5/7,5/8,5 Mts</t>
+  </si>
+  <si>
+    <t>Casilla Rural La Criolla de 4.5 Metros  2 camas</t>
+  </si>
+  <si>
+    <t>Casilla Rural La Criolla de 5.5 Metros 4 camas</t>
+  </si>
+  <si>
+    <t>Casilla Rural La Criolla de 6.5 Metros 4 camas</t>
+  </si>
+  <si>
+    <t>Casilla Rural La Criolla de 7.5 Metros 6 camas</t>
+  </si>
+  <si>
+    <t>Casilla Rural La Criolla de 8.5 Metros 6 camas</t>
+  </si>
+  <si>
+    <t>La criolla</t>
+  </si>
+  <si>
+    <t>Casilla rodante De Ruta 4 Camas oportunidad</t>
+  </si>
+  <si>
+    <t>Casilla Rural Fm 7300 6 Camas</t>
+  </si>
+  <si>
+    <t>CASILLAS DISPONBLES NUEVAS Y USADAS.
+NO DUDES EN CONSULTAR POR NUEVAS O OTROS MODELOS.
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+Cuentan con TERMOTANQUE, TOLDO, BAULERA, INSTALACIÓN DE AGUA y ELÉCTRICA.
+AISLANTE: TERGOPOL.
+Disponibles en distintas medidas:
+✔️ 4,5 m – 2 camas - 14800 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 5,5 m – 4 camas - 16300 + IVA - DISPONIBLE ENTREGA INMEDIATA
+✔️ 6,5 m – 4 camas - 19900 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 7,5 m – 6 camas - 21400 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 8,5 m – 6 camas - 24000 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ Modelos personalizados a pedido
+Para mas informacion sobre financiacion, precios y fotos de cada casilla en especifico no dudes en consultarnos.
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+CASILLAS RURALES - "La Criolla" - Linea 2026
+Cuentan con TERMOTANQUE, TOLDO, BAULERA, INSTALACIÓN DE AGUA y ELÉCTRICA.
+AISLANTE: TERGOPOL.
+Disponibles en distintas medidas:
+✔️ 4,5 m – 2 camas - 14800 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 5,5 m – 4 camas - 16300 + IVA - DISPONIBLE ENTREGA INMEDIATA
+✔️ 6,5 m – 4 camas - 19900 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 7,5 m – 6 camas - 21400 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ 8,5 m – 6 camas - 24000 + IVA - sin stock ENTREGA 30 40 dias 
+✔️ Modelos personalizados a pedido
+Para mas informacion sobre financiacion, precios y fotos de cada casilla en especifico no dudes en consultarnos.
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+Visita nuestro perfil para conocer nuestro stock.
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.
+USADO
+Visita nuestro perfil para conocer nuestro stock.
+Contamos con más de 300 implementos disponibles
+📍 Liniers 1035, Hernando, Córdoba
+TOTI CONTI S.A. – Ferreteria, repuestos y maquinarias agricolas DESDE 1979 acompañando al productor.</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>Tucumán, Argentina</t>
+  </si>
+  <si>
+    <t>Otra marca --&gt;</t>
+  </si>
+  <si>
+    <t>Tractor Deutz Ax 120</t>
   </si>
 </sst>
 </file>
@@ -172,10 +715,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,153 +1057,2202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B912D2-C765-407B-ACA8-767B34B38FC8}">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" customWidth="1"/>
-    <col min="2" max="2" width="17.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" customWidth="1"/>
-    <col min="13" max="13" width="12.88671875" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="62.44140625" style="1" customWidth="1"/>
+    <col min="6" max="9" width="11.5546875" style="1"/>
+    <col min="10" max="10" width="16.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" style="1"/>
+    <col min="13" max="13" width="12.88671875" style="1" customWidth="1"/>
+    <col min="14" max="15" width="11.5546875" style="1"/>
+    <col min="16" max="16" width="21.33203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="17" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="G2" s="1">
+        <v>20000</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="1">
+        <v>2015</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1">
+        <v>17500</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1">
+        <v>1999</v>
+      </c>
+      <c r="N3" s="1">
+        <v>88</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1">
+        <v>28000</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1988</v>
+      </c>
+      <c r="N4" s="1">
+        <v>120</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2">
-        <v>17500</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1">
+        <v>15000</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="1">
+        <v>65</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
+        <v>23000</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1989</v>
+      </c>
+      <c r="N6" s="1">
+        <v>160</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
+        <v>14750</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="1">
+        <v>85</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="1">
+        <v>55</v>
+      </c>
+      <c r="N8" s="1">
+        <v>55</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <v>24000</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1982</v>
+      </c>
+      <c r="N9" s="1">
+        <v>105</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1">
+        <v>38000</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="1">
+        <v>160</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
+        <v>60000</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1780</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1996</v>
+      </c>
+      <c r="N11" s="1">
+        <v>180</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
+        <v>15300</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N12" s="1">
+        <v>65</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1">
+        <v>17150</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="N13" s="1">
+        <v>25</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N14" s="1">
+        <v>25</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="1">
+        <v>7300</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="1">
+        <v>11000</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="1">
+        <v>11000</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="1">
+        <v>25000</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="1">
+        <v>7500</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="1">
+        <v>14000</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2600</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2600</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2">
-        <v>1999</v>
-      </c>
-      <c r="N2">
+      <c r="E31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="1">
+        <v>8400</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="1">
+        <v>35000</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="1">
+        <v>9000</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="1">
+        <v>14900</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="1">
+        <v>6900</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2800</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="F39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5200</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3">
-        <v>20000</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="C40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5100</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>2015</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>8</v>
+      <c r="C41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2025</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="1">
+        <v>6200</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M45" s="1">
+        <v>2024</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2750</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3500</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="M47" s="1">
+        <v>2022</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2850</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3200</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1800</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="1">
+        <v>14800</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M52" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="1">
+        <v>16300</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M53" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="1">
+        <v>19100</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M54" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="1">
+        <v>21400</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M55" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="1">
+        <v>24000</v>
+      </c>
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M56" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="1">
+        <v>24000</v>
+      </c>
+      <c r="H57" s="1">
+        <v>38</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M57" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="1">
+        <v>7500</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1">
+        <v>30000</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M59" s="1">
+        <v>2026</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
